--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd (ddd)"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -105,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -182,6 +183,7 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2348,6 +2350,19 @@
           <t>UI/UX Designer, .NET Developer</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="n">
+        <v>46146</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Stage 1 (foundations) complete: schema delta + EF migration + portal cookie scheme + IPublicUserPropertyAccessor scoping spine + IEmailSender/IFileStorage abstractions + DwsClaimsTransformation scheme isolation + cross-scheme integration tests. UI/registration/MFA still ahead in Stage 2. (2026-05-04)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">

--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -2360,7 +2360,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Stage 1 (foundations) complete: schema delta + EF migration + portal cookie scheme + IPublicUserPropertyAccessor scoping spine + IEmailSender/IFileStorage abstractions + DwsClaimsTransformation scheme isolation + cross-scheme integration tests. UI/registration/MFA still ahead in Stage 2. (2026-05-04)</t>
+          <t>Stage 1 + Stage 2a complete: foundations + portal area shell + register + email confirm + login + dashboard placeholder. MFA + recovery codes + lockout + reset still ahead in Stage 2b. (2026-05-04)</t>
         </is>
       </c>
     </row>

--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,6 +184,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -679,11 +680,11 @@
         </is>
       </c>
       <c r="I3" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J3" s="22" t="inlineStr">
         <is>
-          <t>Team mobilised; ongoing iteration with client. (2026-04-29)</t>
+          <t>Team mobilised; ongoing weekly iteration with client. Client review positive.</t>
         </is>
       </c>
     </row>
@@ -767,11 +768,11 @@
         </is>
       </c>
       <c r="I5" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>Architecture aligned with DWS feedback (Design Amendment 002 incorporated). (2026-04-29)</t>
+          <t>Architecture aligned with DWS feedback; Design Amendments 001 &amp; 002 incorporated.</t>
         </is>
       </c>
     </row>
@@ -811,11 +812,11 @@
         </is>
       </c>
       <c r="I6" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>Plan baselined; RAID log not yet maintained in tooling. (2026-04-29)</t>
+          <t>Plan baselined and now refreshed; RAID log still not maintained in tooling.</t>
         </is>
       </c>
     </row>
@@ -882,11 +883,11 @@
         </is>
       </c>
       <c r="I8" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>Subscription in use; demo RG provisioned and torn down. Landing zone not formalised. (2026-04-29)</t>
+          <t>Now deployed on client Azure ('Purple Blue') tenant. Landing zone / governance not yet formalised.</t>
         </is>
       </c>
     </row>
@@ -988,11 +989,11 @@
         </is>
       </c>
       <c r="I11" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J11" s="22" t="inlineStr">
         <is>
-          <t>App Service B1 + Linux runtime + zip-deploy proven via demo. Blob storage not yet configured. (2026-04-29)</t>
+          <t>App Service + GitHub Actions deploy operational on client Azure. Storage abstraction (IFileStorage) in code with local-disk impl; Azure Blob binding pending.</t>
         </is>
       </c>
     </row>
@@ -1032,11 +1033,11 @@
         </is>
       </c>
       <c r="I12" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>Entra ID OpenID Connect handler stubbed in Program.cs; tenant app registration pending. (2026-04-29)</t>
+          <t>Entra ID OpenID Connect handler stubbed in Program.cs; tenant app registration pending.</t>
         </is>
       </c>
     </row>
@@ -1316,11 +1317,11 @@
         </is>
       </c>
       <c r="I21" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>Entity models for Property, FileMaster, Entitlement, Workflow*, Letter*, Audit, etc. defined. (2026-04-29)</t>
+          <t>55+ entities incl. Workflow*, Letter*, Calculator/Lawfulness, MFA, Objection, Audit. Schema near complete (22 EF migrations).</t>
         </is>
       </c>
     </row>
@@ -1404,11 +1405,11 @@
         </is>
       </c>
       <c r="I23" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>Repositories implemented for Property, FileMaster, Owner, Address, Forestation. More to come. (2026-04-29)</t>
+          <t>Repositories for Property, FileMaster, Owner, Address, Forestation, FieldAndCrop, DamCalculation.</t>
         </is>
       </c>
     </row>
@@ -1448,11 +1449,11 @@
         </is>
       </c>
       <c r="I24" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>WorkflowService, LetterService, AuditService, IdentitySeeder live. Service layer growing. (2026-04-29)</t>
+          <t>WorkflowService, LetterService, AuditService, NotificationService, plus CalculatorService (Dam/SAPWAT/SFRA) and LawfulnessAssessmentService (GWCA + general principles) all live.</t>
         </is>
       </c>
     </row>
@@ -1492,11 +1493,11 @@
         </is>
       </c>
       <c r="I25" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>79 unit + ViewModel tests passing; integration tests need a SQL fixture. (2026-04-29)</t>
+          <t>~339 unit + ViewModel test cases passing (was 79). Integration tests still need a SQL fixture.</t>
         </is>
       </c>
     </row>
@@ -1689,6 +1690,19 @@
           <t>Senior .NET Developer, Business Analyst</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Protest/Objection + ObjectionGrounds models; ExternalPortal Objection + Response flows live. Client 'Appeal/Objection' terminology adopted. Lifecycle UI iterating.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1726,11 +1740,11 @@
         </is>
       </c>
       <c r="I31" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>AuditLogs table + AuditService write immutable rows on every workflow advance, letter issue, login, etc. (2026-04-29)</t>
+          <t>AuditLogs + AuditService write immutable rows on every workflow advance, letter issue, login, etc.</t>
         </is>
       </c>
     </row>
@@ -2161,11 +2175,11 @@
         </is>
       </c>
       <c r="I45" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>Sidebar layout matches latest wireframes; user-admin row actions inlined. Iterating per Solution-Look-and-Feel.html. (2026-04-29)</t>
+          <t>Sidebar layout per latest wireframes; DWS brand palette; Appendix D dam calculator inputs added to DamCalculation views (BUG-019).</t>
         </is>
       </c>
     </row>
@@ -2352,15 +2366,15 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I51" s="26" t="n">
-        <v>46146</v>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>46175</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Stage 1 + Stage 2a complete: foundations + portal area shell + register + email confirm + login + dashboard placeholder. MFA + recovery codes + lockout + reset still ahead in Stage 2b. (2026-05-04)</t>
+          <t>Stages 1/2a/2b complete: register, email confirm, login, dashboard, case status+history, document upload, objection/response, full MFA (TOTP, SMS OTP, recovery codes, trusted device, lockout).</t>
         </is>
       </c>
     </row>
@@ -2394,6 +2408,19 @@
           <t>.NET Developer</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Read-only case status view + workflow history live in external portal.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -2425,6 +2452,19 @@
           <t>.NET Developer</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>External-portal document upload live (DocumentController + IFileStorage, SHA-256 hash, virus-scan status field). Internal V&amp;V control-point document upload now in design.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2454,6 +2494,19 @@
       <c r="G54" s="7" t="inlineStr">
         <is>
           <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NotificationService wired for in-app + email (SMTP / logging sender); per-state-change triggers in workflow.</t>
         </is>
       </c>
     </row>
@@ -2551,11 +2604,11 @@
         </is>
       </c>
       <c r="I57" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J57" s="22" t="inlineStr">
         <is>
-          <t>Entra ID OpenID Connect path stubbed alongside Identity local accounts. Full SSO not yet wired end-to-end. (2026-04-29)</t>
+          <t>Entra ID OIDC path stubbed alongside Identity local accounts; full SSO not yet wired end-to-end.</t>
         </is>
       </c>
     </row>
@@ -2595,11 +2648,11 @@
         </is>
       </c>
       <c r="I58" s="21" t="n">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="J58" s="22" t="inlineStr">
         <is>
-          <t>DwsRoles + DwsPolicies enforce role-based access (SystemAdmin / NationalManager / RegionalManager / Validator / Capturer / ReadOnly). HDI flag captured on user profile. (2026-04-29)</t>
+          <t>DwsRoles + DwsPolicies enforce RBAC (SystemAdmin/NationalManager/RegionalManager/Validator/Capturer/ReadOnly). HDI indicator on user profile (AddIsHdiToApplicationUser migration).</t>
         </is>
       </c>
     </row>

--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I53" s="27" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>External-portal document upload live (DocumentController + IFileStorage, SHA-256 hash, virus-scan status field). Internal V&amp;V control-point document upload now in design.</t>
+          <t>Internal staff document upload live (DocumentController: scope+RBAC+audit, virus-scan status, SHA-256) alongside external portal. Documents are gated workflow evidence: DocumentEvidenceGuard blocks CP2 (Title Deed+SG Diagram) and CP3 (WARMS report); CP11 re-checks the Appendix A set. eWULAAS push deferred (fields ready).</t>
         </is>
       </c>
     </row>

--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -1317,11 +1317,11 @@
         </is>
       </c>
       <c r="I21" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>55+ entities incl. Workflow*, Letter*, Calculator/Lawfulness, MFA, Objection, Audit. Schema near complete (22 EF migrations).</t>
+          <t>64 EF entities incl. Workflow*, Letter*, Calculator/Lawfulness, PublicUser*, Objection, CatchmentArea, Property status/parent FK, HDI.</t>
         </is>
       </c>
     </row>
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="I24" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>WorkflowService, LetterService, AuditService, NotificationService, plus CalculatorService (Dam/SAPWAT/SFRA) and LawfulnessAssessmentService (GWCA + general principles) all live.</t>
+          <t>WorkflowService, LetterService (QuestPDF), LawfulnessAssessmentService, CalculatorService, AuditService, NotificationService all live. OUTSTANDING: SignatureService (e-sig+X.509) and IntegrationService (eWULAAS push) not yet built; due-date reminder automation not built.</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="I25" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>~339 unit + ViewModel test cases passing (was 79). Integration tests still need a SQL fixture.</t>
+          <t>~441 unit/integration tests passing; SQL-Server integration harness added but most service tests still on EF-InMemory (X-01). Next: migrate off InMemory + add Playwright E2E.</t>
         </is>
       </c>
     </row>
@@ -1564,11 +1564,11 @@
         </is>
       </c>
       <c r="I27" s="21" t="n">
-        <v>46141</v>
+        <v>46181</v>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>WorkflowEngine: CP1.1 -&gt; CP9 state machine with 6 transition guards (CP2/3/4/5/8/9). (2026-04-29)</t>
+          <t>CP1-&gt;CP9 state machine + S33(2) skip track, guards, blocking reasons. Note: CP1 sub-steps 1.1-1.7 not yet decomposed into guarded sub-states; WF-01 concurrency token outstanding.</t>
         </is>
       </c>
     </row>
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="I28" s="21" t="n">
-        <v>46141</v>
+        <v>46181</v>
       </c>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>10 letter templates wired (S35 L1, L1A, L2, L2A, L3, L4A, L4&amp;5, S33(2), S33(3)(a), S33(3)(b)) rendering via QuestPDF. (2026-04-29)</t>
+          <t>10 letter templates (S35 L1/1A/2/2A/3/4A/4&amp;5, S33(2)/S33(3a)/S33(3b)). WF-02 unique-index + atomic issuance outstanding.</t>
         </is>
       </c>
     </row>
@@ -1696,11 +1696,11 @@
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Protest/Objection + ObjectionGrounds models; ExternalPortal Objection + Response flows live. Client 'Appeal/Objection' terminology adopted. Lifecycle UI iterating.</t>
+          <t>Objection lifecycle live in External Portal (Protest renamed). OUTSTANDING: objection supporting-doc uploads; remove legacy Protest/ProtestDocument models.</t>
         </is>
       </c>
     </row>
@@ -1740,11 +1740,11 @@
         </is>
       </c>
       <c r="I31" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>AuditLogs + AuditService write immutable rows on every workflow advance, letter issue, login, etc.</t>
+          <t>AuditService writes immutable AuditLog rows on workflow advance, letter issue, document upload. Immutability is insert-only by convention.</t>
         </is>
       </c>
     </row>
@@ -1805,6 +1805,19 @@
           <t>Senior .NET Developer, Business Analyst</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6 org-scoped reports (Catchment Progress, Letter Tracking, Validation Summary, User Activity, Portal Usage, Integration Health-shell).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1836,6 +1849,19 @@
           <t>.NET Developer</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Ad-hoc query builder not started. Report filter binds via querystring but no filter-form UI in views yet.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -1867,6 +1893,19 @@
           <t>UI/UX Designer, .NET Developer</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Org-scoped home dashboard with self-hosted D3 v7 charts (no CDN), DWS palette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1896,6 +1935,19 @@
       <c r="G36" s="7" t="inlineStr">
         <is>
           <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CSV/Excel/PDF exporters live (18/18 export combinations validated); formula-injection neutralised.</t>
         </is>
       </c>
     </row>
@@ -2111,6 +2163,19 @@
           <t>.NET Developer</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Advanced notification &amp; reminder system (overdue-letter escalation, hosted BackgroundService) not built — WBS-7 automation stream ~15%.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2175,11 +2240,11 @@
         </is>
       </c>
       <c r="I45" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>Sidebar layout per latest wireframes; DWS brand palette; Appendix D dam calculator inputs added to DamCalculation views (BUG-019).</t>
+          <t>Sidebar layout per wireframes, DWS brand palette applied. OUTSTANDING (8.2 mobile-responsive, 8.3 WCAG 2.1 AA) not started; report filter forms missing.</t>
         </is>
       </c>
     </row>
@@ -2370,11 +2435,11 @@
         </is>
       </c>
       <c r="I51" s="27" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Stages 1/2a/2b complete: register, email confirm, login, dashboard, case status+history, document upload, objection/response, full MFA (TOTP, SMS OTP, recovery codes, trusted device, lockout).</t>
+          <t>Register, email confirm, login, dashboard, separate PublicPortalScheme cookie + isolation tests.</t>
         </is>
       </c>
     </row>
@@ -2410,15 +2475,15 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I52" s="27" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Read-only case status view + workflow history live in external portal.</t>
+          <t>Read-only case view live; workflow state + history not yet surfaced (WorkflowState hardcoded null in portal VM).</t>
         </is>
       </c>
     </row>
@@ -2458,11 +2523,11 @@
         </is>
       </c>
       <c r="I53" s="27" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Internal staff document upload live (DocumentController: scope+RBAC+audit, virus-scan status, SHA-256) alongside external portal. Documents are gated workflow evidence: DocumentEvidenceGuard blocks CP2 (Title Deed+SG Diagram) and CP3 (WARMS report); CP11 re-checks the Appendix A set. eWULAAS push deferred (fields ready).</t>
+          <t>Internal + external document upload (scope+RBAC+audit, magic-byte+vocab+size). Virus-scan status=Pending stub; real scanner outstanding.</t>
         </is>
       </c>
     </row>
@@ -2502,11 +2567,11 @@
         </is>
       </c>
       <c r="I54" s="27" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>NotificationService wired for in-app + email (SMTP / logging sender); per-state-change triggers in workflow.</t>
+          <t>NotificationService wired for in-app + email on letters/replies/claim decisions. OUTSTANDING: generic state-change notifications, bell/inbox UI, MFA recovery codes, real SMS provider.</t>
         </is>
       </c>
     </row>
@@ -2604,11 +2669,11 @@
         </is>
       </c>
       <c r="I57" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J57" s="22" t="inlineStr">
         <is>
-          <t>Entra ID OIDC path stubbed alongside Identity local accounts; full SSO not yet wired end-to-end.</t>
+          <t>Entra ID OIDC handler stubbed alongside Identity; full SSO not completed.</t>
         </is>
       </c>
     </row>
@@ -2648,11 +2713,11 @@
         </is>
       </c>
       <c r="I58" s="21" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="J58" s="22" t="inlineStr">
         <is>
-          <t>DwsRoles + DwsPolicies enforce RBAC (SystemAdmin/NationalManager/RegionalManager/Validator/Capturer/ReadOnly). HDI indicator on user profile (AddIsHdiToApplicationUser migration).</t>
+          <t>DwsRoles + DwsPolicies enforce RBAC; org scope catchment&gt;WMA&gt;province; HDI indicator on internal + public profiles.</t>
         </is>
       </c>
     </row>
@@ -2686,6 +2751,19 @@
           <t>Security Architect, Business Analyst</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>POPIA compliance review + data-classification controls not started.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -2715,6 +2793,19 @@
       <c r="G60" s="7" t="inlineStr">
         <is>
           <t>Security Architect</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>4 remediation waves: DOC-01 ship-blocker fixed; AUTH-01/BUG-030/X-04/DOC-03 fixed; magic-byte upload validation. OUTSTANDING: WF-01/WF-02 concurrency, virus-scan gate, path-traversal hardening, threat model.</t>
         </is>
       </c>
     </row>

--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="I24" s="21" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>WorkflowService, LetterService (QuestPDF), LawfulnessAssessmentService, CalculatorService, AuditService, NotificationService all live. OUTSTANDING: SignatureService (e-sig+X.509) and IntegrationService (eWULAAS push) not yet built; due-date reminder automation not built.</t>
+          <t>WorkflowService, LetterService (QuestPDF), LawfulnessAssessmentService, CalculatorService, AuditService, NotificationService all live. OUTSTANDING: SignatureService (e-sig+X.509) and IntegrationService (eWULAAS push) not yet built; due-date reminder automation not built. 2026-06-11: Admin console added — OrganisationalUnits, GWCAs + proclamation-rule mgmt (IsActive toggle), reference-data CRUD with FK-delete protection.</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="I25" s="21" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>~441 unit/integration tests passing; SQL-Server integration harness added but most service tests still on EF-InMemory (X-01). Next: migrate off InMemory + add Playwright E2E.</t>
+          <t>~441 unit/integration tests passing; SQL-Server integration harness added but most service tests still on EF-InMemory (X-01). Next: migrate off InMemory + add Playwright E2E. 2026-06-11: 526 unit/integration + 35 Playwright E2E tests green (full V&amp;V process journey, state-machine guards, S33(2) track, dam calculator, admin console).</t>
         </is>
       </c>
     </row>
@@ -1564,11 +1564,11 @@
         </is>
       </c>
       <c r="I27" s="21" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>CP1-&gt;CP9 state machine + S33(2) skip track, guards, blocking reasons. Note: CP1 sub-steps 1.1-1.7 not yet decomposed into guarded sub-states; WF-01 concurrency token outstanding.</t>
+          <t>CP1-&gt;CP9 state machine + S33(2) skip track, guards, blocking reasons. Note: CP1 sub-steps 1.1-1.7 not yet decomposed into guarded sub-states; WF-01 concurrency token outstanding. 2026-06-11: state machine E2E-verified end-to-end through the UI; engine hardened — direct advance into letter states now refused (must go via IssueLetter).</t>
         </is>
       </c>
     </row>
@@ -2864,6 +2864,19 @@
       <c r="G62" s="7" t="inlineStr">
         <is>
           <t>QA Lead, .NET Developer</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I62" s="26" t="n">
+        <v>46184</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-06-11: Playwright E2E harness at 35 tests incl. complete S35 V&amp;V journey and Appendix D dam calculator verification.</t>
         </is>
       </c>
     </row>

--- a/Project rollout plan.xlsx
+++ b/Project rollout plan.xlsx
@@ -2709,15 +2709,15 @@
       </c>
       <c r="H58" s="20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I58" s="21" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="J58" s="22" t="inlineStr">
         <is>
-          <t>DwsRoles + DwsPolicies enforce RBAC; org scope catchment&gt;WMA&gt;province; HDI indicator on internal + public profiles.</t>
+          <t>DwsRoles + DwsPolicies enforce RBAC; org scope catchment&gt;WMA&gt;province; HDI indicator on internal + public profiles. 2026-06-11: HDI indicator confirmed live (user create/edit). Internal-staff TOTP MFA shipped: opt-in authenticator enrolment with QR + recovery codes, RequiresTwoFactor login flow, admin MFA reset; stale feat/hdi-and-mfa branch deleted (superseded).</t>
         </is>
       </c>
     </row>
